--- a/artfynd/A 1999-2023 artfynd.xlsx
+++ b/artfynd/A 1999-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1999-2023 artfynd.xlsx
+++ b/artfynd/A 1999-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6819799</v>
+        <v>6819552</v>
       </c>
       <c r="B2" t="n">
-        <v>95521</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224363</v>
+        <v>219875</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -711,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545103.496263661</v>
+        <v>544910</v>
       </c>
       <c r="R2" t="n">
-        <v>6413652.526733185</v>
+        <v>6413655</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -744,19 +743,9 @@
           <t>2013-06-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-06-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,50 +772,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6819552</v>
+        <v>6819559</v>
       </c>
       <c r="B3" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219875</v>
+        <v>219955</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bränna, norra hagen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544909.9692716493</v>
+        <v>545015</v>
       </c>
       <c r="R3" t="n">
-        <v>6413654.613560094</v>
+        <v>6413688</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,19 +849,9 @@
           <t>2013-06-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-06-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,37 +878,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6819557</v>
+        <v>6819560</v>
       </c>
       <c r="B4" t="n">
-        <v>96252</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223591</v>
+        <v>221849</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -935,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545015.1454669473</v>
+        <v>545015</v>
       </c>
       <c r="R4" t="n">
-        <v>6413687.714558266</v>
+        <v>6413688</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,19 +946,9 @@
           <t>2013-06-25</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-06-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,59 +975,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6819559</v>
+        <v>6819557</v>
       </c>
       <c r="B5" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99036</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219955</v>
+        <v>223591</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bränna, norra hagen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545015.1454669473</v>
+        <v>545015</v>
       </c>
       <c r="R5" t="n">
-        <v>6413687.714558266</v>
+        <v>6413688</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,19 +1043,9 @@
           <t>2013-06-25</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2013-06-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,39 +1072,30 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6819560</v>
+        <v>6819800</v>
       </c>
       <c r="B6" t="n">
-        <v>104404</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99154</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221849</v>
+        <v>223619</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Ängsnattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Platanthera bifolia subsp. bifolia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1168,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545015.1454669473</v>
+        <v>545015</v>
       </c>
       <c r="R6" t="n">
-        <v>6413687.714558266</v>
+        <v>6413688</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,19 +1136,9 @@
           <t>2013-06-25</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2013-06-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,15 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6819800</v>
+        <v>6819799</v>
       </c>
       <c r="B7" t="n">
-        <v>96368</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,16 +1176,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223619</v>
+        <v>224363</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ängsnattviol</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. bifolia</t>
+          <t>Lycopodium annotinum subsp. annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1276,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545015.1454669473</v>
+        <v>545103</v>
       </c>
       <c r="R7" t="n">
-        <v>6413687.714558266</v>
+        <v>6413653</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,19 +1229,9 @@
           <t>2013-06-25</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2013-06-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,59 +1258,44 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97295953</v>
+        <v>6819561</v>
       </c>
       <c r="B8" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>102563</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219955</v>
+        <v>265350</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Vanligt jungfrulin</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Polygala vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bränna, norra hagen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545015.1335366666</v>
+        <v>545015</v>
       </c>
       <c r="R8" t="n">
-        <v>6413688.778521557</v>
+        <v>6413688</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,29 +1320,14 @@
           <t>Horn</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>E-Kin-0308</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
           <t>2013-06-25</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2013-06-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,7 +1342,7 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Monika Sunhede</t>
+          <t>Urban Ekstam</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -1470,11 +1350,7 @@
           <t>Urban Ekstam</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1999-2023 artfynd.xlsx
+++ b/artfynd/A 1999-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6819552</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6819559</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6819560</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6819557</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6819800</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6819799</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,8 +1386,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6819561</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>